--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA0C025-55AB-411F-9F67-0D758788C312}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC5588C-F8F5-4D6A-808E-BE88D84E9A0E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -935,7 +935,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -994,17 +994,6 @@
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1282,7 +1271,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1724,21 +1713,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3651,80 +3625,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EBC75A05-1183-4793-98D9-648A8C14341C}" name="Programacion" displayName="Programacion" ref="A1:AS231" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
-  <autoFilter ref="A1:AS231" xr:uid="{0B78E266-A4D5-4544-882A-2577FC206A12}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6C28F9A-93A4-4C10-9549-03F57954427E}" name="Programacion" displayName="Programacion" ref="A1:AS231" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
+  <autoFilter ref="A1:AS231" xr:uid="{AC61BF39-04C6-4AD5-A60E-00A37D0DEFF3}"/>
   <tableColumns count="45">
-    <tableColumn id="1" xr3:uid="{B093B8D8-CF52-4774-98DB-5D297C7A7558}" name="CENTRO COSTO" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{D0AB6A41-84A1-4D6B-A012-EB591EB2B73A}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{FAFA3306-C69E-4D0D-9368-3645CB176FA4}" name="RUBRO" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{963F1A6D-33F1-4271-933A-CD41D6E8C148}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{C68F5381-6EF3-4D53-BCF7-418F86E2BD92}" name="META" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{0AD7AA54-0483-4341-B81E-0757E7E65DC9}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{81CB6C74-973F-4E81-B877-E59AD78DC56D}" name="CLASIFICADOR" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{E5531284-5333-488A-8131-23B1D639EDE3}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
-    <tableColumn id="21" xr3:uid="{5C1F3ABC-4191-4F8B-B878-B4EBEFAD6697}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
-    <tableColumn id="9" xr3:uid="{04861EDB-A42B-4115-AA06-7652BC69C662}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
-    <tableColumn id="22" xr3:uid="{18EF6EB4-19FE-4B2F-A4E8-CD09F6A48A1D}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
-    <tableColumn id="10" xr3:uid="{C9125B55-EE2C-42C5-81E6-E4DDDB8B1515}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
-    <tableColumn id="23" xr3:uid="{4044A467-77E3-4238-BCFC-9044760841EB}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
-    <tableColumn id="11" xr3:uid="{EA4FE435-BA7B-4B11-AEAD-6D3F7A3FB758}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
-    <tableColumn id="24" xr3:uid="{09F6709F-13EA-469A-9346-930908B059CC}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
-    <tableColumn id="12" xr3:uid="{D27FE9B3-459D-4DE6-A426-923578BE7EA0}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
-    <tableColumn id="25" xr3:uid="{20F6B0E4-F1C3-4F3C-B292-C174D869F03D}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
-    <tableColumn id="13" xr3:uid="{371C7C24-9D6A-4DC5-BCA9-2943DD635992}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
-    <tableColumn id="26" xr3:uid="{155570EF-B138-4FCE-AF7A-495911221454}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
-    <tableColumn id="14" xr3:uid="{673BA08D-DE3F-4DD2-B630-933CF673D20B}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
-    <tableColumn id="27" xr3:uid="{1BB605AF-0414-4FA9-BFC1-07D82141742E}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
-    <tableColumn id="15" xr3:uid="{AE06C596-6E8F-4E27-9745-DFDB717AEE1E}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
-    <tableColumn id="28" xr3:uid="{3540F4D2-DDED-4228-897F-852253E330A8}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
-    <tableColumn id="16" xr3:uid="{2E973430-E144-4647-8721-2B4C3862E17E}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
-    <tableColumn id="29" xr3:uid="{A8860BF2-5189-4653-8598-3E1C5E0776C6}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
-    <tableColumn id="17" xr3:uid="{876BAF7A-FF7A-46C6-9401-627E14715176}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
-    <tableColumn id="30" xr3:uid="{13D50EA9-0AE6-4A1C-8C9F-0B3AD09A9F62}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
-    <tableColumn id="18" xr3:uid="{ECD65AB5-CBEA-4327-86BA-AC8CD76BB0B0}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
-    <tableColumn id="32" xr3:uid="{98FC4DB0-B527-466F-A075-727948D7DC9D}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
-    <tableColumn id="19" xr3:uid="{975BC5DC-A196-4724-B718-05D831F01777}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
-    <tableColumn id="33" xr3:uid="{A0827F02-EB1B-4EEB-B815-796F236270AB}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
-    <tableColumn id="20" xr3:uid="{6F01D1F0-9CA6-4A64-9D1E-9D5EAAAC8B41}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
+    <tableColumn id="1" xr3:uid="{BB0E1B95-0A2C-4DCB-894C-42EF1CA5F14B}" name="CENTRO COSTO" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{8F2A9E64-7BC0-4FAB-8FAE-A5DEFC95D0AE}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{C8DE7E21-DB00-4992-BB1F-9FDE8953C6C4}" name="RUBRO" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{9FED56C3-7FE1-4461-9CD6-357251AF2E83}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{7F57CB0C-BD6C-4DD0-B7AD-27D82D65C6D0}" name="META" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{42D20511-F0E1-4A7F-A143-91128B0000FC}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{F8675303-CDF7-4DC5-A26D-F81D66FC5D73}" name="CLASIFICADOR" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{477C7BA3-E03E-4FB3-B366-8FDC798E4A0D}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
+    <tableColumn id="21" xr3:uid="{7762ACBB-B906-4003-BA83-65789981DDD3}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
+    <tableColumn id="9" xr3:uid="{8B8C5ED8-0A7D-40E1-B6B7-808367005877}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
+    <tableColumn id="22" xr3:uid="{A42A20C2-F382-427F-A1FF-ACE232C9D386}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
+    <tableColumn id="10" xr3:uid="{0DA94D64-CCEC-41F3-A080-B2051296A750}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
+    <tableColumn id="23" xr3:uid="{A00E6823-5954-437D-BF85-5AA129CB69F1}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
+    <tableColumn id="11" xr3:uid="{C2FBD9B7-CBEE-4943-9F11-D48FCEBB138B}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
+    <tableColumn id="24" xr3:uid="{358A542F-FDC5-4C85-920E-0556622EB5F7}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
+    <tableColumn id="12" xr3:uid="{F76228F6-EAAD-46DE-A9E7-AD8A5CEF2C28}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
+    <tableColumn id="25" xr3:uid="{4A79AE4A-7499-45F2-8B86-B510FAEFF23E}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
+    <tableColumn id="13" xr3:uid="{5B7A768F-D28C-4C73-A327-DFA3AAA4EC11}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
+    <tableColumn id="26" xr3:uid="{1201AFA4-0C72-4C4E-B56B-3906E5ABAFB2}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
+    <tableColumn id="14" xr3:uid="{9B015179-092D-4C73-B3DE-646FD908D60A}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
+    <tableColumn id="27" xr3:uid="{1E0350FC-CF08-4D0E-BF46-514CEDD9377C}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
+    <tableColumn id="15" xr3:uid="{9B867D59-6171-476C-A75B-589942678828}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
+    <tableColumn id="28" xr3:uid="{6F5E3C90-4B66-4F1D-B899-597F4ECF89DC}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
+    <tableColumn id="16" xr3:uid="{8C796D55-4F4B-46A5-AA02-D6F6D1217FDC}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
+    <tableColumn id="29" xr3:uid="{FF9C8327-7AAC-4E8D-98DE-2F9243B9D02A}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
+    <tableColumn id="17" xr3:uid="{CE5A40BB-7B34-4ADB-AE50-365E2D510446}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
+    <tableColumn id="30" xr3:uid="{D5633501-0C4C-4351-807A-4ACB426E2FCE}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
+    <tableColumn id="18" xr3:uid="{9117AA2C-CC22-419D-8C44-8D5449EBBDD9}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
+    <tableColumn id="32" xr3:uid="{7934D674-426A-4D31-BCC9-8701DC19D12C}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
+    <tableColumn id="19" xr3:uid="{97F11E3E-3169-4340-B858-9BFD0488B5F5}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
+    <tableColumn id="33" xr3:uid="{B3B048B9-A8D2-40BE-97CA-269C8198CEF7}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
+    <tableColumn id="20" xr3:uid="{7C2B10EA-E4E6-4D0D-B724-41C406DA8338}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{2B218BEE-92B4-46F2-9189-D24E80B2EDAA}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
+    <tableColumn id="37" xr3:uid="{6FE6F51F-0BE0-4CD6-A4F4-5842EAE06A7C}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{B7C871FB-6034-4962-B835-53E6AEDCFE16}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
+    <tableColumn id="43" xr3:uid="{254D517C-8049-4B4F-AC42-997219C767B6}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{B6AE396E-B33A-4ECA-8FF3-4AA2F2887357}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
+    <tableColumn id="36" xr3:uid="{BDDCD88C-F15F-4BA9-88FF-0473F6B42F93}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{3D263C70-9655-42D3-83E0-121B197A5CB7}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
+    <tableColumn id="44" xr3:uid="{20CC68B7-98FD-43ED-B8CB-F105CCC178D8}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{3B49780E-340B-4895-8ED9-DFC600FF7666}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
+    <tableColumn id="39" xr3:uid="{871613F3-F82F-422D-87BF-683C7F360619}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{AC8F02C5-0DA3-46B4-BEAE-873E15FD432D}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
+    <tableColumn id="45" xr3:uid="{BABF8CF9-C67C-44E5-8FF5-59A5E9460B53}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{2448A604-8474-4C7A-981C-BD4A894325A2}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
+    <tableColumn id="38" xr3:uid="{5AE8D867-9058-4B25-8009-FD9C29AE284A}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{5297690A-7BDA-4C2B-9D09-DD748DCDEFEE}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
+    <tableColumn id="46" xr3:uid="{34976FE4-B885-49C9-AD46-1725B0E9DA4F}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{1E253DDF-F7CD-4AFC-B78D-D6171985033C}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
+    <tableColumn id="41" xr3:uid="{BE572DB6-2395-416A-8056-28455CC1C244}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{81D1FBBD-740A-4E28-B7F9-45202678A6F6}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
+    <tableColumn id="31" xr3:uid="{8BBA7FDD-E960-4B14-8614-C3CE1BC01534}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{493CDFCC-1870-4FFA-94FD-E71EC2E10EB1}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
+    <tableColumn id="40" xr3:uid="{7F4D0DC5-8FC7-451B-AD0C-A3B2B435C6D0}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{6AF3BC77-776B-41E6-B622-085ED3B29BB3}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
+    <tableColumn id="35" xr3:uid="{3FA97412-29D8-4987-98BF-3D8FF0966C42}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{B3DCD6BE-F636-4805-ABDA-00AC64F79530}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
+    <tableColumn id="34" xr3:uid="{8FF1594D-FDFA-4624-A47F-8993916C1232}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5295,7 +5269,9 @@
       <c r="T12" s="17"/>
       <c r="U12" s="17"/>
       <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
+      <c r="W12" s="17">
+        <v>2096.16</v>
+      </c>
       <c r="X12" s="17">
         <v>2400</v>
       </c>
@@ -5332,7 +5308,7 @@
       </c>
       <c r="AL12" s="17">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>2096.16</v>
       </c>
       <c r="AM12" s="17">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -5356,11 +5332,11 @@
       </c>
       <c r="AR12" s="17">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>2096.16</v>
       </c>
       <c r="AS12" s="17">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>2096.16</v>
       </c>
       <c r="AT12" s="116"/>
     </row>
@@ -6599,7 +6575,9 @@
       <c r="V24" s="17">
         <v>5000</v>
       </c>
-      <c r="W24" s="17"/>
+      <c r="W24" s="17">
+        <v>5000</v>
+      </c>
       <c r="X24" s="17">
         <v>5000</v>
       </c>
@@ -6638,7 +6616,7 @@
       </c>
       <c r="AL24" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AM24" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -6662,11 +6640,11 @@
       </c>
       <c r="AR24" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AS24" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="AT24" s="116"/>
     </row>
@@ -6837,7 +6815,9 @@
       <c r="V26" s="17">
         <v>6000</v>
       </c>
-      <c r="W26" s="17"/>
+      <c r="W26" s="17">
+        <v>6000</v>
+      </c>
       <c r="X26" s="17">
         <v>6000</v>
       </c>
@@ -6880,7 +6860,7 @@
       </c>
       <c r="AL26" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="AM26" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -6904,11 +6884,11 @@
       </c>
       <c r="AR26" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="AS26" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="AT26" s="116"/>
     </row>
@@ -7321,7 +7301,9 @@
       <c r="V30" s="17">
         <v>4000</v>
       </c>
-      <c r="W30" s="17"/>
+      <c r="W30" s="17">
+        <v>4000</v>
+      </c>
       <c r="X30" s="17">
         <v>4000</v>
       </c>
@@ -7364,7 +7346,7 @@
       </c>
       <c r="AL30" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AM30" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -7388,11 +7370,11 @@
       </c>
       <c r="AR30" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AS30" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AT30" s="116"/>
     </row>
@@ -9160,85 +9142,85 @@
       <c r="G47" s="124" t="s">
         <v>259</v>
       </c>
-      <c r="H47" s="148"/>
-      <c r="I47" s="148"/>
-      <c r="J47" s="148"/>
-      <c r="K47" s="148"/>
-      <c r="L47" s="148"/>
-      <c r="M47" s="148"/>
-      <c r="N47" s="148"/>
-      <c r="O47" s="148"/>
-      <c r="P47" s="148"/>
-      <c r="Q47" s="148"/>
-      <c r="R47" s="148"/>
-      <c r="S47" s="148"/>
-      <c r="T47" s="148"/>
-      <c r="U47" s="148"/>
-      <c r="V47" s="148"/>
-      <c r="W47" s="148"/>
-      <c r="X47" s="148"/>
-      <c r="Y47" s="148"/>
-      <c r="Z47" s="148"/>
-      <c r="AA47" s="148"/>
-      <c r="AB47" s="148"/>
-      <c r="AC47" s="148"/>
-      <c r="AD47" s="148">
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="33"/>
+      <c r="Y47" s="33"/>
+      <c r="Z47" s="33"/>
+      <c r="AA47" s="33"/>
+      <c r="AB47" s="33"/>
+      <c r="AC47" s="33"/>
+      <c r="AD47" s="33">
         <v>3950</v>
       </c>
-      <c r="AE47" s="148"/>
-      <c r="AF47" s="148">
+      <c r="AE47" s="33"/>
+      <c r="AF47" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>3950</v>
       </c>
-      <c r="AG47" s="148">
+      <c r="AG47" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH47" s="148">
+      <c r="AH47" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI47" s="148">
+      <c r="AI47" s="33">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ47" s="148">
+      <c r="AJ47" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK47" s="148">
+      <c r="AK47" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AL47" s="148">
+      <c r="AL47" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AM47" s="148">
+      <c r="AM47" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>3950</v>
       </c>
-      <c r="AN47" s="149">
+      <c r="AN47" s="21">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO47" s="149">
+      <c r="AO47" s="21">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP47" s="149">
+      <c r="AP47" s="21">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ47" s="149">
+      <c r="AQ47" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>3950</v>
       </c>
-      <c r="AR47" s="149">
+      <c r="AR47" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AS47" s="148">
+      <c r="AS47" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
@@ -9372,85 +9354,85 @@
       <c r="G49" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="H49" s="148"/>
-      <c r="I49" s="148"/>
-      <c r="J49" s="148"/>
-      <c r="K49" s="148"/>
-      <c r="L49" s="148"/>
-      <c r="M49" s="148"/>
-      <c r="N49" s="148"/>
-      <c r="O49" s="148"/>
-      <c r="P49" s="148"/>
-      <c r="Q49" s="148"/>
-      <c r="R49" s="148"/>
-      <c r="S49" s="148"/>
-      <c r="T49" s="148"/>
-      <c r="U49" s="148"/>
-      <c r="V49" s="148"/>
-      <c r="W49" s="148"/>
-      <c r="X49" s="148"/>
-      <c r="Y49" s="148"/>
-      <c r="Z49" s="148"/>
-      <c r="AA49" s="148"/>
-      <c r="AB49" s="148"/>
-      <c r="AC49" s="148"/>
-      <c r="AD49" s="148">
+      <c r="H49" s="33"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="33"/>
+      <c r="M49" s="33"/>
+      <c r="N49" s="33"/>
+      <c r="O49" s="33"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="33"/>
+      <c r="S49" s="33"/>
+      <c r="T49" s="33"/>
+      <c r="U49" s="33"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="33"/>
+      <c r="Y49" s="33"/>
+      <c r="Z49" s="33"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="33"/>
+      <c r="AC49" s="33"/>
+      <c r="AD49" s="33">
         <v>3665</v>
       </c>
-      <c r="AE49" s="148"/>
-      <c r="AF49" s="148">
+      <c r="AE49" s="33"/>
+      <c r="AF49" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>3665</v>
       </c>
-      <c r="AG49" s="148">
+      <c r="AG49" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH49" s="148">
+      <c r="AH49" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI49" s="148">
+      <c r="AI49" s="33">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ49" s="148">
+      <c r="AJ49" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK49" s="148">
+      <c r="AK49" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AL49" s="148">
+      <c r="AL49" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AM49" s="148">
+      <c r="AM49" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>3665</v>
       </c>
-      <c r="AN49" s="149">
+      <c r="AN49" s="21">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO49" s="149">
+      <c r="AO49" s="21">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP49" s="149">
+      <c r="AP49" s="21">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ49" s="149">
+      <c r="AQ49" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>3665</v>
       </c>
-      <c r="AR49" s="149">
+      <c r="AR49" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AS49" s="148">
+      <c r="AS49" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
@@ -9584,85 +9566,85 @@
       <c r="G51" s="147" t="s">
         <v>121</v>
       </c>
-      <c r="H51" s="148"/>
-      <c r="I51" s="148"/>
-      <c r="J51" s="148"/>
-      <c r="K51" s="148"/>
-      <c r="L51" s="148"/>
-      <c r="M51" s="148"/>
-      <c r="N51" s="148"/>
-      <c r="O51" s="148"/>
-      <c r="P51" s="148"/>
-      <c r="Q51" s="148"/>
-      <c r="R51" s="148"/>
-      <c r="S51" s="148"/>
-      <c r="T51" s="148"/>
-      <c r="U51" s="148"/>
-      <c r="V51" s="148"/>
-      <c r="W51" s="148"/>
-      <c r="X51" s="148"/>
-      <c r="Y51" s="148"/>
-      <c r="Z51" s="148"/>
-      <c r="AA51" s="148"/>
-      <c r="AB51" s="148"/>
-      <c r="AC51" s="148"/>
-      <c r="AD51" s="148">
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+      <c r="M51" s="33"/>
+      <c r="N51" s="33"/>
+      <c r="O51" s="33"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="33"/>
+      <c r="S51" s="33"/>
+      <c r="T51" s="33"/>
+      <c r="U51" s="33"/>
+      <c r="V51" s="33"/>
+      <c r="W51" s="33"/>
+      <c r="X51" s="33"/>
+      <c r="Y51" s="33"/>
+      <c r="Z51" s="33"/>
+      <c r="AA51" s="33"/>
+      <c r="AB51" s="33"/>
+      <c r="AC51" s="33"/>
+      <c r="AD51" s="33">
         <v>5465.91</v>
       </c>
-      <c r="AE51" s="148"/>
-      <c r="AF51" s="148">
+      <c r="AE51" s="33"/>
+      <c r="AF51" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>5465.91</v>
       </c>
-      <c r="AG51" s="148">
+      <c r="AG51" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH51" s="148">
+      <c r="AH51" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI51" s="148">
+      <c r="AI51" s="33">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ51" s="148">
+      <c r="AJ51" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK51" s="148">
+      <c r="AK51" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AL51" s="148">
+      <c r="AL51" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AM51" s="148">
+      <c r="AM51" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>5465.91</v>
       </c>
-      <c r="AN51" s="149">
+      <c r="AN51" s="21">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO51" s="149">
+      <c r="AO51" s="21">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP51" s="149">
+      <c r="AP51" s="21">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ51" s="149">
+      <c r="AQ51" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>5465.91</v>
       </c>
-      <c r="AR51" s="149">
+      <c r="AR51" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AS51" s="148">
+      <c r="AS51" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
@@ -10509,10 +10491,10 @@
       </c>
       <c r="U59" s="31"/>
       <c r="V59" s="31">
-        <v>1080</v>
+        <v>1200</v>
       </c>
       <c r="W59" s="31">
-        <v>1080</v>
+        <v>1200</v>
       </c>
       <c r="X59" s="31">
         <v>1080</v>
@@ -10532,7 +10514,7 @@
       <c r="AE59" s="31"/>
       <c r="AF59" s="18">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>12880</v>
+        <v>13000</v>
       </c>
       <c r="AG59" s="19">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -10552,11 +10534,11 @@
       </c>
       <c r="AK59" s="19">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>3240</v>
+        <v>3360</v>
       </c>
       <c r="AL59" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>1080</v>
+        <v>1200</v>
       </c>
       <c r="AM59" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -10576,15 +10558,15 @@
       </c>
       <c r="AQ59" s="20">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>6480</v>
+        <v>6600</v>
       </c>
       <c r="AR59" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>1080</v>
+        <v>1200</v>
       </c>
       <c r="AS59" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>7480</v>
+        <v>7600</v>
       </c>
       <c r="AT59" s="116"/>
     </row>
@@ -11891,7 +11873,9 @@
       <c r="V71" s="31">
         <v>6000</v>
       </c>
-      <c r="W71" s="31"/>
+      <c r="W71" s="31">
+        <v>6000</v>
+      </c>
       <c r="X71" s="31">
         <v>6000</v>
       </c>
@@ -11934,7 +11918,7 @@
       </c>
       <c r="AL71" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="AM71" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -11958,11 +11942,11 @@
       </c>
       <c r="AR71" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="AS71" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="AT71" s="116"/>
     </row>
@@ -14915,7 +14899,9 @@
       <c r="V98" s="39">
         <v>5000</v>
       </c>
-      <c r="W98" s="39"/>
+      <c r="W98" s="39">
+        <v>5000</v>
+      </c>
       <c r="X98" s="39">
         <v>5000</v>
       </c>
@@ -14958,7 +14944,7 @@
       </c>
       <c r="AL98" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AM98" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -14982,11 +14968,11 @@
       </c>
       <c r="AR98" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AS98" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AT98" s="116"/>
     </row>
@@ -15257,7 +15243,9 @@
       <c r="V101" s="39">
         <v>5000</v>
       </c>
-      <c r="W101" s="39"/>
+      <c r="W101" s="39">
+        <v>5000</v>
+      </c>
       <c r="X101" s="39">
         <v>5000</v>
       </c>
@@ -15294,7 +15282,7 @@
       </c>
       <c r="AL101" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AM101" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -15318,11 +15306,11 @@
       </c>
       <c r="AR101" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AS101" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AT101" s="116"/>
     </row>
@@ -16395,7 +16383,9 @@
       <c r="V111" s="49">
         <v>8500</v>
       </c>
-      <c r="W111" s="49"/>
+      <c r="W111" s="49">
+        <v>8500</v>
+      </c>
       <c r="X111" s="49"/>
       <c r="Y111" s="49"/>
       <c r="Z111" s="49"/>
@@ -16430,7 +16420,7 @@
       </c>
       <c r="AL111" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>8500</v>
+        <v>17000</v>
       </c>
       <c r="AM111" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -16454,11 +16444,11 @@
       </c>
       <c r="AR111" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>8500</v>
+        <v>17000</v>
       </c>
       <c r="AS111" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>34000</v>
+        <v>42500</v>
       </c>
       <c r="AT111" s="116"/>
     </row>
@@ -16977,7 +16967,9 @@
       <c r="V116" s="49">
         <v>4000</v>
       </c>
-      <c r="W116" s="49"/>
+      <c r="W116" s="49">
+        <v>4000</v>
+      </c>
       <c r="X116" s="49">
         <v>4000</v>
       </c>
@@ -17016,7 +17008,7 @@
       </c>
       <c r="AL116" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AM116" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -17040,11 +17032,11 @@
       </c>
       <c r="AR116" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AS116" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="AT116" s="116"/>
     </row>
@@ -17207,7 +17199,9 @@
       <c r="V118" s="49">
         <v>7500</v>
       </c>
-      <c r="W118" s="49"/>
+      <c r="W118" s="49">
+        <v>7500</v>
+      </c>
       <c r="X118" s="49"/>
       <c r="Y118" s="49"/>
       <c r="Z118" s="49"/>
@@ -17242,7 +17236,7 @@
       </c>
       <c r="AL118" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="AM118" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -17266,11 +17260,11 @@
       </c>
       <c r="AR118" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="AS118" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>22500</v>
+        <v>30000</v>
       </c>
       <c r="AT118" s="116"/>
     </row>
@@ -17750,87 +17744,87 @@
       <c r="G123" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="H123" s="148"/>
-      <c r="I123" s="148"/>
-      <c r="J123" s="148"/>
-      <c r="K123" s="148"/>
-      <c r="L123" s="148"/>
-      <c r="M123" s="148"/>
-      <c r="N123" s="148"/>
-      <c r="O123" s="148"/>
-      <c r="P123" s="148"/>
-      <c r="Q123" s="148"/>
-      <c r="R123" s="148"/>
-      <c r="S123" s="148"/>
-      <c r="T123" s="148"/>
-      <c r="U123" s="148"/>
-      <c r="V123" s="148">
+      <c r="H123" s="33"/>
+      <c r="I123" s="33"/>
+      <c r="J123" s="33"/>
+      <c r="K123" s="33"/>
+      <c r="L123" s="33"/>
+      <c r="M123" s="33"/>
+      <c r="N123" s="33"/>
+      <c r="O123" s="33"/>
+      <c r="P123" s="33"/>
+      <c r="Q123" s="33"/>
+      <c r="R123" s="33"/>
+      <c r="S123" s="33"/>
+      <c r="T123" s="33"/>
+      <c r="U123" s="33"/>
+      <c r="V123" s="33">
         <v>800</v>
       </c>
-      <c r="W123" s="148">
+      <c r="W123" s="33">
         <v>800</v>
       </c>
-      <c r="X123" s="148"/>
-      <c r="Y123" s="148"/>
-      <c r="Z123" s="148"/>
-      <c r="AA123" s="148"/>
-      <c r="AB123" s="148"/>
-      <c r="AC123" s="148"/>
-      <c r="AD123" s="148"/>
-      <c r="AE123" s="148"/>
-      <c r="AF123" s="148">
+      <c r="X123" s="33"/>
+      <c r="Y123" s="33"/>
+      <c r="Z123" s="33"/>
+      <c r="AA123" s="33"/>
+      <c r="AB123" s="33"/>
+      <c r="AC123" s="33"/>
+      <c r="AD123" s="33"/>
+      <c r="AE123" s="33"/>
+      <c r="AF123" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>800</v>
       </c>
-      <c r="AG123" s="148">
+      <c r="AG123" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH123" s="148">
+      <c r="AH123" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI123" s="148">
+      <c r="AI123" s="33">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ123" s="148">
+      <c r="AJ123" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK123" s="148">
+      <c r="AK123" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>800</v>
       </c>
-      <c r="AL123" s="148">
+      <c r="AL123" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>800</v>
       </c>
-      <c r="AM123" s="148">
+      <c r="AM123" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN123" s="149">
+      <c r="AN123" s="21">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO123" s="149">
+      <c r="AO123" s="21">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP123" s="149">
+      <c r="AP123" s="21">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ123" s="149">
+      <c r="AQ123" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>800</v>
       </c>
-      <c r="AR123" s="149">
+      <c r="AR123" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>800</v>
       </c>
-      <c r="AS123" s="148">
+      <c r="AS123" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>800</v>
       </c>
@@ -17858,97 +17852,97 @@
       <c r="G124" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H124" s="148"/>
-      <c r="I124" s="148"/>
-      <c r="J124" s="148"/>
-      <c r="K124" s="148"/>
-      <c r="L124" s="148"/>
-      <c r="M124" s="148"/>
-      <c r="N124" s="148"/>
-      <c r="O124" s="148"/>
-      <c r="P124" s="148"/>
-      <c r="Q124" s="148"/>
-      <c r="R124" s="148"/>
-      <c r="S124" s="148"/>
-      <c r="T124" s="148"/>
-      <c r="U124" s="148"/>
-      <c r="V124" s="148">
+      <c r="H124" s="33"/>
+      <c r="I124" s="33"/>
+      <c r="J124" s="33"/>
+      <c r="K124" s="33"/>
+      <c r="L124" s="33"/>
+      <c r="M124" s="33"/>
+      <c r="N124" s="33"/>
+      <c r="O124" s="33"/>
+      <c r="P124" s="33"/>
+      <c r="Q124" s="33"/>
+      <c r="R124" s="33"/>
+      <c r="S124" s="33"/>
+      <c r="T124" s="33"/>
+      <c r="U124" s="33"/>
+      <c r="V124" s="33">
         <v>540</v>
       </c>
-      <c r="W124" s="148">
+      <c r="W124" s="33">
         <v>540</v>
       </c>
-      <c r="X124" s="148"/>
-      <c r="Y124" s="148"/>
-      <c r="Z124" s="148"/>
-      <c r="AA124" s="148"/>
-      <c r="AB124" s="148"/>
-      <c r="AC124" s="148"/>
-      <c r="AD124" s="148"/>
-      <c r="AE124" s="148"/>
-      <c r="AF124" s="148">
+      <c r="X124" s="33"/>
+      <c r="Y124" s="33"/>
+      <c r="Z124" s="33"/>
+      <c r="AA124" s="33"/>
+      <c r="AB124" s="33"/>
+      <c r="AC124" s="33"/>
+      <c r="AD124" s="33"/>
+      <c r="AE124" s="33"/>
+      <c r="AF124" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>540</v>
       </c>
-      <c r="AG124" s="148">
+      <c r="AG124" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH124" s="148">
+      <c r="AH124" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI124" s="148">
+      <c r="AI124" s="33">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ124" s="148">
+      <c r="AJ124" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK124" s="148">
+      <c r="AK124" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>540</v>
       </c>
-      <c r="AL124" s="148">
+      <c r="AL124" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>540</v>
       </c>
-      <c r="AM124" s="148">
+      <c r="AM124" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN124" s="149">
+      <c r="AN124" s="21">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO124" s="149">
+      <c r="AO124" s="21">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP124" s="149">
+      <c r="AP124" s="21">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ124" s="149">
+      <c r="AQ124" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>540</v>
       </c>
-      <c r="AR124" s="149">
+      <c r="AR124" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>540</v>
       </c>
-      <c r="AS124" s="148">
+      <c r="AS124" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>540</v>
       </c>
       <c r="AT124" s="116"/>
     </row>
     <row r="125" spans="1:46" ht="30" x14ac:dyDescent="0.25">
-      <c r="A125" s="150" t="s">
+      <c r="A125" s="132" t="s">
         <v>124</v>
       </c>
-      <c r="B125" s="150" t="s">
+      <c r="B125" s="132" t="s">
         <v>294</v>
       </c>
       <c r="C125" s="36" t="s">
@@ -17957,94 +17951,94 @@
       <c r="D125" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="E125" s="151">
+      <c r="E125" s="104">
         <v>39</v>
       </c>
-      <c r="F125" s="152">
+      <c r="F125" s="105">
         <v>2.2999999999999998</v>
       </c>
       <c r="G125" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="H125" s="148"/>
-      <c r="I125" s="148"/>
-      <c r="J125" s="148"/>
-      <c r="K125" s="148"/>
-      <c r="L125" s="148"/>
-      <c r="M125" s="148"/>
-      <c r="N125" s="148"/>
-      <c r="O125" s="148"/>
-      <c r="P125" s="148"/>
-      <c r="Q125" s="148"/>
-      <c r="R125" s="148"/>
-      <c r="S125" s="148"/>
-      <c r="T125" s="148"/>
-      <c r="U125" s="148"/>
-      <c r="V125" s="148"/>
-      <c r="W125" s="148"/>
-      <c r="X125" s="148">
+      <c r="H125" s="33"/>
+      <c r="I125" s="33"/>
+      <c r="J125" s="33"/>
+      <c r="K125" s="33"/>
+      <c r="L125" s="33"/>
+      <c r="M125" s="33"/>
+      <c r="N125" s="33"/>
+      <c r="O125" s="33"/>
+      <c r="P125" s="33"/>
+      <c r="Q125" s="33"/>
+      <c r="R125" s="33"/>
+      <c r="S125" s="33"/>
+      <c r="T125" s="33"/>
+      <c r="U125" s="33"/>
+      <c r="V125" s="33"/>
+      <c r="W125" s="33"/>
+      <c r="X125" s="33">
         <v>1000</v>
       </c>
-      <c r="Y125" s="148"/>
-      <c r="Z125" s="148"/>
-      <c r="AA125" s="148"/>
-      <c r="AB125" s="148"/>
-      <c r="AC125" s="148"/>
-      <c r="AD125" s="148"/>
-      <c r="AE125" s="148"/>
-      <c r="AF125" s="148">
+      <c r="Y125" s="33"/>
+      <c r="Z125" s="33"/>
+      <c r="AA125" s="33"/>
+      <c r="AB125" s="33"/>
+      <c r="AC125" s="33"/>
+      <c r="AD125" s="33"/>
+      <c r="AE125" s="33"/>
+      <c r="AF125" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>1000</v>
       </c>
-      <c r="AG125" s="148">
+      <c r="AG125" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH125" s="148">
+      <c r="AH125" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI125" s="148">
+      <c r="AI125" s="33">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ125" s="148">
+      <c r="AJ125" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK125" s="148">
+      <c r="AK125" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>1000</v>
       </c>
-      <c r="AL125" s="148">
+      <c r="AL125" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AM125" s="148">
+      <c r="AM125" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN125" s="149">
+      <c r="AN125" s="21">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO125" s="149">
+      <c r="AO125" s="21">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP125" s="149">
+      <c r="AP125" s="21">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ125" s="149">
+      <c r="AQ125" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>1000</v>
       </c>
-      <c r="AR125" s="149">
+      <c r="AR125" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AS125" s="148">
+      <c r="AS125" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
@@ -18157,10 +18151,10 @@
       <c r="AT126" s="116"/>
     </row>
     <row r="127" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A127" s="150" t="s">
+      <c r="A127" s="132" t="s">
         <v>124</v>
       </c>
-      <c r="B127" s="150" t="s">
+      <c r="B127" s="132" t="s">
         <v>295</v>
       </c>
       <c r="C127" s="46" t="s">
@@ -18169,202 +18163,206 @@
       <c r="D127" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="E127" s="151">
+      <c r="E127" s="104">
         <v>39</v>
       </c>
-      <c r="F127" s="152">
+      <c r="F127" s="105">
         <v>2.2999999999999998</v>
       </c>
       <c r="G127" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="H127" s="148"/>
-      <c r="I127" s="148"/>
-      <c r="J127" s="148"/>
-      <c r="K127" s="148"/>
-      <c r="L127" s="148"/>
-      <c r="M127" s="148"/>
-      <c r="N127" s="148"/>
-      <c r="O127" s="148"/>
-      <c r="P127" s="148"/>
-      <c r="Q127" s="148"/>
-      <c r="R127" s="148"/>
-      <c r="S127" s="148"/>
-      <c r="T127" s="148"/>
-      <c r="U127" s="148"/>
-      <c r="V127" s="148"/>
-      <c r="W127" s="148"/>
-      <c r="X127" s="148">
+      <c r="H127" s="33"/>
+      <c r="I127" s="33"/>
+      <c r="J127" s="33"/>
+      <c r="K127" s="33"/>
+      <c r="L127" s="33"/>
+      <c r="M127" s="33"/>
+      <c r="N127" s="33"/>
+      <c r="O127" s="33"/>
+      <c r="P127" s="33"/>
+      <c r="Q127" s="33"/>
+      <c r="R127" s="33"/>
+      <c r="S127" s="33"/>
+      <c r="T127" s="33"/>
+      <c r="U127" s="33"/>
+      <c r="V127" s="33">
         <v>2700</v>
       </c>
-      <c r="Y127" s="148"/>
-      <c r="Z127" s="148"/>
-      <c r="AA127" s="148"/>
-      <c r="AB127" s="148"/>
-      <c r="AC127" s="148"/>
-      <c r="AD127" s="148"/>
-      <c r="AE127" s="148"/>
-      <c r="AF127" s="148">
+      <c r="W127" s="33">
+        <v>2700</v>
+      </c>
+      <c r="X127" s="33"/>
+      <c r="Y127" s="33"/>
+      <c r="Z127" s="33"/>
+      <c r="AA127" s="33"/>
+      <c r="AB127" s="33"/>
+      <c r="AC127" s="33"/>
+      <c r="AD127" s="33"/>
+      <c r="AE127" s="33"/>
+      <c r="AF127" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>2700</v>
       </c>
-      <c r="AG127" s="148">
+      <c r="AG127" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH127" s="148">
+      <c r="AH127" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI127" s="148">
+      <c r="AI127" s="33">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ127" s="148">
+      <c r="AJ127" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK127" s="148">
+      <c r="AK127" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>2700</v>
       </c>
-      <c r="AL127" s="148">
+      <c r="AL127" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AM127" s="148">
+        <v>2700</v>
+      </c>
+      <c r="AM127" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN127" s="149">
+      <c r="AN127" s="21">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO127" s="149">
+      <c r="AO127" s="21">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP127" s="149">
+      <c r="AP127" s="21">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ127" s="149">
+      <c r="AQ127" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>2700</v>
       </c>
-      <c r="AR127" s="149">
+      <c r="AR127" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AS127" s="148">
+        <v>2700</v>
+      </c>
+      <c r="AS127" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="AT127" s="116"/>
     </row>
-    <row r="128" spans="1:46" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="150" t="s">
+    <row r="128" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A128" s="132" t="s">
         <v>124</v>
       </c>
-      <c r="B128" s="150" t="s">
+      <c r="B128" s="132" t="s">
         <v>296</v>
       </c>
-      <c r="C128" s="36" t="s">
-        <v>74</v>
+      <c r="C128" s="128" t="s">
+        <v>265</v>
       </c>
       <c r="D128" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="E128" s="151">
+      <c r="E128" s="104">
         <v>39</v>
       </c>
-      <c r="F128" s="152">
+      <c r="F128" s="105">
         <v>2.2999999999999998</v>
       </c>
       <c r="G128" s="103" t="s">
         <v>193</v>
       </c>
-      <c r="H128" s="148"/>
-      <c r="I128" s="148"/>
-      <c r="J128" s="148"/>
-      <c r="K128" s="148"/>
-      <c r="L128" s="148"/>
-      <c r="M128" s="148"/>
-      <c r="N128" s="148"/>
-      <c r="O128" s="148"/>
-      <c r="P128" s="148"/>
-      <c r="Q128" s="148"/>
-      <c r="R128" s="148"/>
-      <c r="S128" s="148"/>
-      <c r="T128" s="148"/>
-      <c r="U128" s="148"/>
-      <c r="V128" s="148"/>
-      <c r="W128" s="148"/>
-      <c r="X128" s="148">
+      <c r="H128" s="33"/>
+      <c r="I128" s="33"/>
+      <c r="J128" s="33"/>
+      <c r="K128" s="33"/>
+      <c r="L128" s="33"/>
+      <c r="M128" s="33"/>
+      <c r="N128" s="33"/>
+      <c r="O128" s="33"/>
+      <c r="P128" s="33"/>
+      <c r="Q128" s="33"/>
+      <c r="R128" s="33"/>
+      <c r="S128" s="33"/>
+      <c r="T128" s="33"/>
+      <c r="U128" s="33"/>
+      <c r="V128" s="33">
         <v>150</v>
       </c>
-      <c r="Y128" s="148"/>
-      <c r="Z128" s="148"/>
-      <c r="AA128" s="148"/>
-      <c r="AB128" s="148"/>
-      <c r="AC128" s="148"/>
-      <c r="AD128" s="148"/>
-      <c r="AE128" s="148"/>
-      <c r="AF128" s="148">
+      <c r="W128" s="33">
+        <v>150</v>
+      </c>
+      <c r="X128" s="33"/>
+      <c r="Y128" s="33"/>
+      <c r="Z128" s="33"/>
+      <c r="AA128" s="33"/>
+      <c r="AB128" s="33"/>
+      <c r="AC128" s="33"/>
+      <c r="AD128" s="33"/>
+      <c r="AE128" s="33"/>
+      <c r="AF128" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>150</v>
       </c>
-      <c r="AG128" s="148">
+      <c r="AG128" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AH128" s="148">
+      <c r="AH128" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</f>
         <v>0</v>
       </c>
-      <c r="AI128" s="148">
+      <c r="AI128" s="33">
         <f>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AJ128" s="148">
+      <c r="AJ128" s="33">
         <f>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AK128" s="148">
+      <c r="AK128" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
         <v>150</v>
       </c>
-      <c r="AL128" s="148">
+      <c r="AL128" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AM128" s="148">
+        <v>150</v>
+      </c>
+      <c r="AM128" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AN128" s="149">
+      <c r="AN128" s="21">
         <f>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
         <v>0</v>
       </c>
-      <c r="AO128" s="149">
+      <c r="AO128" s="21">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AP128" s="149">
+      <c r="AP128" s="21">
         <f>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</f>
         <v>0</v>
       </c>
-      <c r="AQ128" s="149">
+      <c r="AQ128" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
         <v>150</v>
       </c>
-      <c r="AR128" s="149">
+      <c r="AR128" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
-      </c>
-      <c r="AS128" s="148">
+        <v>150</v>
+      </c>
+      <c r="AS128" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AT128" s="116"/>
     </row>
@@ -18511,10 +18509,10 @@
       <c r="T130" s="33"/>
       <c r="U130" s="33"/>
       <c r="V130" s="33"/>
-      <c r="W130" s="33"/>
-      <c r="X130" s="33">
+      <c r="W130" s="33">
         <v>1200</v>
       </c>
+      <c r="X130" s="33"/>
       <c r="Y130" s="33"/>
       <c r="Z130" s="33"/>
       <c r="AA130" s="33"/>
@@ -18524,7 +18522,7 @@
       <c r="AE130" s="33"/>
       <c r="AF130" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="AG130" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -18544,11 +18542,11 @@
       </c>
       <c r="AK130" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="AL130" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AM130" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -18568,15 +18566,15 @@
       </c>
       <c r="AQ130" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="AR130" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AS130" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AT130" s="116"/>
     </row>
@@ -19291,7 +19289,9 @@
       <c r="V137" s="59">
         <v>5000</v>
       </c>
-      <c r="W137" s="59"/>
+      <c r="W137" s="59">
+        <v>5000</v>
+      </c>
       <c r="X137" s="59">
         <v>5000</v>
       </c>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="AL137" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AM137" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -19358,11 +19358,11 @@
       </c>
       <c r="AR137" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AS137" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AT137" s="116"/>
     </row>
@@ -19753,7 +19753,9 @@
       <c r="V141" s="59">
         <v>1730.4</v>
       </c>
-      <c r="W141" s="59"/>
+      <c r="W141" s="59">
+        <v>1730.4</v>
+      </c>
       <c r="X141" s="59">
         <v>1730.4</v>
       </c>
@@ -19796,7 +19798,7 @@
       </c>
       <c r="AL141" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>1730.4</v>
+        <v>3460.8</v>
       </c>
       <c r="AM141" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -19820,11 +19822,11 @@
       </c>
       <c r="AR141" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>1730.4</v>
+        <v>3460.8</v>
       </c>
       <c r="AS141" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>8596</v>
+        <v>10326.4</v>
       </c>
       <c r="AT141" s="116"/>
     </row>
@@ -20103,7 +20105,9 @@
       <c r="V144" s="59">
         <v>5000</v>
       </c>
-      <c r="W144" s="59"/>
+      <c r="W144" s="59">
+        <v>5000</v>
+      </c>
       <c r="X144" s="59">
         <v>5000</v>
       </c>
@@ -20146,7 +20150,7 @@
       </c>
       <c r="AL144" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AM144" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -20170,11 +20174,11 @@
       </c>
       <c r="AR144" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AS144" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AT144" s="116"/>
     </row>
@@ -20341,7 +20345,9 @@
       <c r="V146" s="59">
         <v>5000</v>
       </c>
-      <c r="W146" s="59"/>
+      <c r="W146" s="59">
+        <v>5000</v>
+      </c>
       <c r="X146" s="59">
         <v>5000</v>
       </c>
@@ -20384,7 +20390,7 @@
       </c>
       <c r="AL146" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AM146" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -20408,11 +20414,11 @@
       </c>
       <c r="AR146" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AS146" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AT146" s="116"/>
     </row>
@@ -20475,7 +20481,9 @@
       <c r="V147" s="59">
         <v>4000</v>
       </c>
-      <c r="W147" s="59"/>
+      <c r="W147" s="59">
+        <v>4000</v>
+      </c>
       <c r="X147" s="59">
         <v>4000</v>
       </c>
@@ -20518,7 +20526,7 @@
       </c>
       <c r="AL147" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AM147" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -20542,11 +20550,11 @@
       </c>
       <c r="AR147" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AS147" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="AT147" s="116"/>
     </row>
@@ -20609,7 +20617,9 @@
       <c r="V148" s="59">
         <v>4000</v>
       </c>
-      <c r="W148" s="59"/>
+      <c r="W148" s="59">
+        <v>4000</v>
+      </c>
       <c r="X148" s="59">
         <v>4000</v>
       </c>
@@ -20652,7 +20662,7 @@
       </c>
       <c r="AL148" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AM148" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -20676,11 +20686,11 @@
       </c>
       <c r="AR148" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AS148" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="AT148" s="116"/>
     </row>
@@ -20847,7 +20857,9 @@
       <c r="V150" s="59">
         <v>5000</v>
       </c>
-      <c r="W150" s="59"/>
+      <c r="W150" s="59">
+        <v>5000</v>
+      </c>
       <c r="X150" s="59">
         <v>5000</v>
       </c>
@@ -20890,7 +20902,7 @@
       </c>
       <c r="AL150" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AM150" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -20914,11 +20926,11 @@
       </c>
       <c r="AR150" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AS150" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AT150" s="116"/>
     </row>
@@ -21085,7 +21097,9 @@
       <c r="V152" s="70">
         <v>5000</v>
       </c>
-      <c r="W152" s="70"/>
+      <c r="W152" s="70">
+        <v>5000</v>
+      </c>
       <c r="X152" s="70">
         <v>5000</v>
       </c>
@@ -21128,7 +21142,7 @@
       </c>
       <c r="AL152" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AM152" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -21152,11 +21166,11 @@
       </c>
       <c r="AR152" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="AS152" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AT152" s="116"/>
     </row>
@@ -21199,7 +21213,9 @@
       <c r="V153" s="33">
         <v>7300</v>
       </c>
-      <c r="W153" s="33"/>
+      <c r="W153" s="33">
+        <v>7300</v>
+      </c>
       <c r="X153" s="33"/>
       <c r="Y153" s="33"/>
       <c r="Z153" s="33"/>
@@ -21234,7 +21250,7 @@
       </c>
       <c r="AL153" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="AM153" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -21258,11 +21274,11 @@
       </c>
       <c r="AR153" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="AS153" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="AT153" s="116"/>
     </row>
@@ -23161,7 +23177,9 @@
       <c r="V171" s="88">
         <v>600</v>
       </c>
-      <c r="W171" s="88"/>
+      <c r="W171" s="88">
+        <v>600</v>
+      </c>
       <c r="X171" s="88"/>
       <c r="Y171" s="88"/>
       <c r="Z171" s="88"/>
@@ -23196,7 +23214,7 @@
       </c>
       <c r="AL171" s="88">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AM171" s="88">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -23220,11 +23238,11 @@
       </c>
       <c r="AR171" s="97">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AS171" s="98">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AT171" s="116"/>
     </row>
@@ -24379,7 +24397,9 @@
       <c r="V182" s="88">
         <v>10800</v>
       </c>
-      <c r="W182" s="88"/>
+      <c r="W182" s="88">
+        <v>10800</v>
+      </c>
       <c r="X182" s="88"/>
       <c r="Y182" s="88"/>
       <c r="Z182" s="88"/>
@@ -24414,7 +24434,7 @@
       </c>
       <c r="AL182" s="88">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>10800</v>
+        <v>21600</v>
       </c>
       <c r="AM182" s="88">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -24438,11 +24458,11 @@
       </c>
       <c r="AR182" s="97">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>10800</v>
+        <v>21600</v>
       </c>
       <c r="AS182" s="98">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>32400</v>
+        <v>43200</v>
       </c>
       <c r="AT182" s="116"/>
     </row>
@@ -25043,7 +25063,9 @@
       <c r="V188" s="88">
         <v>7500</v>
       </c>
-      <c r="W188" s="88"/>
+      <c r="W188" s="88">
+        <v>7500</v>
+      </c>
       <c r="X188" s="88">
         <v>7500</v>
       </c>
@@ -25080,7 +25102,7 @@
       </c>
       <c r="AL188" s="88">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="AM188" s="88">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -25104,11 +25126,11 @@
       </c>
       <c r="AR188" s="97">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="AS188" s="98">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>22500</v>
+        <v>30000</v>
       </c>
       <c r="AT188" s="116"/>
     </row>
@@ -29790,7 +29812,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C19:C22 C44 C153:C154 C91 C156 C11 C46:C52 C122 C126 C129:C130" xr:uid="{4D06531F-7FE9-483D-A041-C1A9C9A74CDC}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C19:C22 C44 C153:C154 C91 C156 C11 C46:C52 C122 C126 C129:C130" xr:uid="{2BA797C6-905D-4C45-907B-2CBCCF00F64D}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC5588C-F8F5-4D6A-808E-BE88D84E9A0E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA35FE0-FA7D-4E0B-A465-897B1A3AF324}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3625,80 +3625,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6C28F9A-93A4-4C10-9549-03F57954427E}" name="Programacion" displayName="Programacion" ref="A1:AS231" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
-  <autoFilter ref="A1:AS231" xr:uid="{AC61BF39-04C6-4AD5-A60E-00A37D0DEFF3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4379D5D7-E491-4EF0-874B-AC90C5A291B5}" name="Programacion" displayName="Programacion" ref="A1:AS231" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
+  <autoFilter ref="A1:AS231" xr:uid="{0FB4D070-C7E2-46B5-8A6C-06AEE59ACD90}"/>
   <tableColumns count="45">
-    <tableColumn id="1" xr3:uid="{BB0E1B95-0A2C-4DCB-894C-42EF1CA5F14B}" name="CENTRO COSTO" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{8F2A9E64-7BC0-4FAB-8FAE-A5DEFC95D0AE}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{C8DE7E21-DB00-4992-BB1F-9FDE8953C6C4}" name="RUBRO" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{9FED56C3-7FE1-4461-9CD6-357251AF2E83}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{7F57CB0C-BD6C-4DD0-B7AD-27D82D65C6D0}" name="META" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{42D20511-F0E1-4A7F-A143-91128B0000FC}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{F8675303-CDF7-4DC5-A26D-F81D66FC5D73}" name="CLASIFICADOR" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{477C7BA3-E03E-4FB3-B366-8FDC798E4A0D}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
-    <tableColumn id="21" xr3:uid="{7762ACBB-B906-4003-BA83-65789981DDD3}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
-    <tableColumn id="9" xr3:uid="{8B8C5ED8-0A7D-40E1-B6B7-808367005877}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
-    <tableColumn id="22" xr3:uid="{A42A20C2-F382-427F-A1FF-ACE232C9D386}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
-    <tableColumn id="10" xr3:uid="{0DA94D64-CCEC-41F3-A080-B2051296A750}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
-    <tableColumn id="23" xr3:uid="{A00E6823-5954-437D-BF85-5AA129CB69F1}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
-    <tableColumn id="11" xr3:uid="{C2FBD9B7-CBEE-4943-9F11-D48FCEBB138B}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
-    <tableColumn id="24" xr3:uid="{358A542F-FDC5-4C85-920E-0556622EB5F7}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
-    <tableColumn id="12" xr3:uid="{F76228F6-EAAD-46DE-A9E7-AD8A5CEF2C28}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
-    <tableColumn id="25" xr3:uid="{4A79AE4A-7499-45F2-8B86-B510FAEFF23E}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
-    <tableColumn id="13" xr3:uid="{5B7A768F-D28C-4C73-A327-DFA3AAA4EC11}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
-    <tableColumn id="26" xr3:uid="{1201AFA4-0C72-4C4E-B56B-3906E5ABAFB2}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
-    <tableColumn id="14" xr3:uid="{9B015179-092D-4C73-B3DE-646FD908D60A}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
-    <tableColumn id="27" xr3:uid="{1E0350FC-CF08-4D0E-BF46-514CEDD9377C}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
-    <tableColumn id="15" xr3:uid="{9B867D59-6171-476C-A75B-589942678828}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
-    <tableColumn id="28" xr3:uid="{6F5E3C90-4B66-4F1D-B899-597F4ECF89DC}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
-    <tableColumn id="16" xr3:uid="{8C796D55-4F4B-46A5-AA02-D6F6D1217FDC}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
-    <tableColumn id="29" xr3:uid="{FF9C8327-7AAC-4E8D-98DE-2F9243B9D02A}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
-    <tableColumn id="17" xr3:uid="{CE5A40BB-7B34-4ADB-AE50-365E2D510446}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
-    <tableColumn id="30" xr3:uid="{D5633501-0C4C-4351-807A-4ACB426E2FCE}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
-    <tableColumn id="18" xr3:uid="{9117AA2C-CC22-419D-8C44-8D5449EBBDD9}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
-    <tableColumn id="32" xr3:uid="{7934D674-426A-4D31-BCC9-8701DC19D12C}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
-    <tableColumn id="19" xr3:uid="{97F11E3E-3169-4340-B858-9BFD0488B5F5}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
-    <tableColumn id="33" xr3:uid="{B3B048B9-A8D2-40BE-97CA-269C8198CEF7}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
-    <tableColumn id="20" xr3:uid="{7C2B10EA-E4E6-4D0D-B724-41C406DA8338}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
+    <tableColumn id="1" xr3:uid="{7B3B6329-B6A8-41C6-8A47-33811E936C61}" name="CENTRO COSTO" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{CC48D8C1-3A51-4363-91D1-2A1E3CEFE0BC}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{4DE96993-443B-48CE-86F8-E8F674B1020D}" name="RUBRO" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{EF8FE563-C9E1-413C-B815-E81FD8925059}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{DFDD1491-2D22-4249-AB57-EF0E742E968D}" name="META" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{ABDAB112-A1AC-42A8-B525-CA857A937727}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{605153DD-1014-4119-AB8B-C6342A66D728}" name="CLASIFICADOR" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{F89636D5-3A3F-4D64-888C-6BFA0F373B4B}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
+    <tableColumn id="21" xr3:uid="{33BA320D-13A2-44E3-B13B-DDB7171A4E4E}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
+    <tableColumn id="9" xr3:uid="{E003B81C-841C-4F98-9A28-6F58A39A2119}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
+    <tableColumn id="22" xr3:uid="{4D4139A5-BC30-4281-8D75-52C8552284B0}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
+    <tableColumn id="10" xr3:uid="{EB0E9E95-3FEB-4A99-A702-963C33E90221}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
+    <tableColumn id="23" xr3:uid="{450A2D13-8401-4B9A-9F13-7A574DDE28C2}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
+    <tableColumn id="11" xr3:uid="{9B7B8249-3CDE-4876-A7E2-94AEEA3A6EBF}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
+    <tableColumn id="24" xr3:uid="{3E0333F5-2FCD-4359-90E6-3EA331DF0BFD}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
+    <tableColumn id="12" xr3:uid="{F03C3AC7-047B-42F1-9F90-92E8D62DD027}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
+    <tableColumn id="25" xr3:uid="{4CFF98BC-B7F9-4B33-AB38-3DF59FF81CBE}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
+    <tableColumn id="13" xr3:uid="{3565B8A9-F235-4EB5-B338-5D7BDB124F60}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
+    <tableColumn id="26" xr3:uid="{18B40737-1913-430B-B3FF-6D2172A576C3}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
+    <tableColumn id="14" xr3:uid="{BD702813-CC28-4219-9D5E-DB897992EC7B}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
+    <tableColumn id="27" xr3:uid="{FC7C30F5-BB3D-45B9-83A8-9CE0E1A191FD}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
+    <tableColumn id="15" xr3:uid="{A58807A0-0531-4702-A33B-0ADE30493516}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
+    <tableColumn id="28" xr3:uid="{CE56B1C3-6C6E-4F27-8495-254E85A4F44C}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
+    <tableColumn id="16" xr3:uid="{3B096E1D-FD0F-4966-9A51-8D17F72E5562}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
+    <tableColumn id="29" xr3:uid="{A1BF872C-49F0-4229-9721-E49FAFF55378}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
+    <tableColumn id="17" xr3:uid="{1AF3595E-6420-4C55-A62C-F4723C54E1C3}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
+    <tableColumn id="30" xr3:uid="{78A55D22-7387-43D4-9737-DE2D7B6351BC}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
+    <tableColumn id="18" xr3:uid="{E82BF0A3-9175-461C-93F0-9A9D09EE0E1B}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
+    <tableColumn id="32" xr3:uid="{3DC47D50-861C-4E2A-997A-C07FD852931D}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
+    <tableColumn id="19" xr3:uid="{F2E86A0E-3BC2-4C2F-B107-73E72337A9A3}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
+    <tableColumn id="33" xr3:uid="{38676015-0F58-44D6-B371-9BA81ED28F5A}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
+    <tableColumn id="20" xr3:uid="{CF5DC892-6CDE-42D1-89D3-DEBAF257C463}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{6FE6F51F-0BE0-4CD6-A4F4-5842EAE06A7C}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
+    <tableColumn id="37" xr3:uid="{DFC3F553-23E5-4E02-AD9C-E476F635BA4E}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{254D517C-8049-4B4F-AC42-997219C767B6}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
+    <tableColumn id="43" xr3:uid="{759C49D8-89A2-4302-97E0-8D6822B51A69}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{BDDCD88C-F15F-4BA9-88FF-0473F6B42F93}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
+    <tableColumn id="36" xr3:uid="{EA1BF967-64A6-4E08-B22F-75D5A1D4FDEC}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{20CC68B7-98FD-43ED-B8CB-F105CCC178D8}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
+    <tableColumn id="44" xr3:uid="{7542A2BE-AAE5-4DD2-A67D-6E7216C0A793}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{871613F3-F82F-422D-87BF-683C7F360619}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
+    <tableColumn id="39" xr3:uid="{EF535E8E-0530-47BB-A1C3-D350C565F83C}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{BABF8CF9-C67C-44E5-8FF5-59A5E9460B53}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
+    <tableColumn id="45" xr3:uid="{4934ECE3-79C4-46DD-9108-6C3E7367AD26}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{5AE8D867-9058-4B25-8009-FD9C29AE284A}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
+    <tableColumn id="38" xr3:uid="{95B8D2B7-99B9-47AF-8E67-B75EAE73EFD2}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{34976FE4-B885-49C9-AD46-1725B0E9DA4F}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
+    <tableColumn id="46" xr3:uid="{F5B75DAF-0F8D-40BA-8080-62332BEA8588}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{BE572DB6-2395-416A-8056-28455CC1C244}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
+    <tableColumn id="41" xr3:uid="{B10D1BB6-325A-4C38-AA80-C527D8CF0F09}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{8BBA7FDD-E960-4B14-8614-C3CE1BC01534}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
+    <tableColumn id="31" xr3:uid="{F134A54D-674A-40D1-BE38-E06B3FD38088}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{7F4D0DC5-8FC7-451B-AD0C-A3B2B435C6D0}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
+    <tableColumn id="40" xr3:uid="{281EB04A-D7D4-426E-91C8-2C2EC9EAA03E}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{3FA97412-29D8-4987-98BF-3D8FF0966C42}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
+    <tableColumn id="35" xr3:uid="{B69D19E5-3001-4E2A-8ED7-10901B6F422B}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{8FF1594D-FDFA-4624-A47F-8993916C1232}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
+    <tableColumn id="34" xr3:uid="{45BDA3C3-99AC-48D3-915E-C1E1003EB321}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -18508,7 +18508,9 @@
       <c r="S130" s="33"/>
       <c r="T130" s="33"/>
       <c r="U130" s="33"/>
-      <c r="V130" s="33"/>
+      <c r="V130" s="33">
+        <v>1200</v>
+      </c>
       <c r="W130" s="33">
         <v>1200</v>
       </c>
@@ -18522,7 +18524,7 @@
       <c r="AE130" s="33"/>
       <c r="AF130" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AG130" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -18542,7 +18544,7 @@
       </c>
       <c r="AK130" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AL130" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
@@ -18566,7 +18568,7 @@
       </c>
       <c r="AQ130" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AR130" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
@@ -29812,7 +29814,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C19:C22 C44 C153:C154 C91 C156 C11 C46:C52 C122 C126 C129:C130" xr:uid="{2BA797C6-905D-4C45-907B-2CBCCF00F64D}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C19:C22 C44 C153:C154 C91 C156 C11 C46:C52 C122 C126 C129:C130" xr:uid="{9700AED1-0919-4E15-ABFF-B9233D4F8A59}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA35FE0-FA7D-4E0B-A465-897B1A3AF324}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC88E49-1806-4050-A3A1-715AE2EA4D93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3625,80 +3625,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4379D5D7-E491-4EF0-874B-AC90C5A291B5}" name="Programacion" displayName="Programacion" ref="A1:AS231" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
-  <autoFilter ref="A1:AS231" xr:uid="{0FB4D070-C7E2-46B5-8A6C-06AEE59ACD90}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C11C6284-A82A-41E3-A520-C36651C1A29D}" name="Programacion" displayName="Programacion" ref="A1:AS231" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
+  <autoFilter ref="A1:AS231" xr:uid="{8B1F43D4-8B91-4043-8A5E-AB42FC946F23}"/>
   <tableColumns count="45">
-    <tableColumn id="1" xr3:uid="{7B3B6329-B6A8-41C6-8A47-33811E936C61}" name="CENTRO COSTO" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{CC48D8C1-3A51-4363-91D1-2A1E3CEFE0BC}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{4DE96993-443B-48CE-86F8-E8F674B1020D}" name="RUBRO" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{EF8FE563-C9E1-413C-B815-E81FD8925059}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{DFDD1491-2D22-4249-AB57-EF0E742E968D}" name="META" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{ABDAB112-A1AC-42A8-B525-CA857A937727}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{605153DD-1014-4119-AB8B-C6342A66D728}" name="CLASIFICADOR" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{F89636D5-3A3F-4D64-888C-6BFA0F373B4B}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
-    <tableColumn id="21" xr3:uid="{33BA320D-13A2-44E3-B13B-DDB7171A4E4E}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
-    <tableColumn id="9" xr3:uid="{E003B81C-841C-4F98-9A28-6F58A39A2119}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
-    <tableColumn id="22" xr3:uid="{4D4139A5-BC30-4281-8D75-52C8552284B0}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
-    <tableColumn id="10" xr3:uid="{EB0E9E95-3FEB-4A99-A702-963C33E90221}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
-    <tableColumn id="23" xr3:uid="{450A2D13-8401-4B9A-9F13-7A574DDE28C2}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
-    <tableColumn id="11" xr3:uid="{9B7B8249-3CDE-4876-A7E2-94AEEA3A6EBF}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
-    <tableColumn id="24" xr3:uid="{3E0333F5-2FCD-4359-90E6-3EA331DF0BFD}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
-    <tableColumn id="12" xr3:uid="{F03C3AC7-047B-42F1-9F90-92E8D62DD027}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
-    <tableColumn id="25" xr3:uid="{4CFF98BC-B7F9-4B33-AB38-3DF59FF81CBE}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
-    <tableColumn id="13" xr3:uid="{3565B8A9-F235-4EB5-B338-5D7BDB124F60}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
-    <tableColumn id="26" xr3:uid="{18B40737-1913-430B-B3FF-6D2172A576C3}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
-    <tableColumn id="14" xr3:uid="{BD702813-CC28-4219-9D5E-DB897992EC7B}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
-    <tableColumn id="27" xr3:uid="{FC7C30F5-BB3D-45B9-83A8-9CE0E1A191FD}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
-    <tableColumn id="15" xr3:uid="{A58807A0-0531-4702-A33B-0ADE30493516}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
-    <tableColumn id="28" xr3:uid="{CE56B1C3-6C6E-4F27-8495-254E85A4F44C}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
-    <tableColumn id="16" xr3:uid="{3B096E1D-FD0F-4966-9A51-8D17F72E5562}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
-    <tableColumn id="29" xr3:uid="{A1BF872C-49F0-4229-9721-E49FAFF55378}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
-    <tableColumn id="17" xr3:uid="{1AF3595E-6420-4C55-A62C-F4723C54E1C3}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
-    <tableColumn id="30" xr3:uid="{78A55D22-7387-43D4-9737-DE2D7B6351BC}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
-    <tableColumn id="18" xr3:uid="{E82BF0A3-9175-461C-93F0-9A9D09EE0E1B}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
-    <tableColumn id="32" xr3:uid="{3DC47D50-861C-4E2A-997A-C07FD852931D}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
-    <tableColumn id="19" xr3:uid="{F2E86A0E-3BC2-4C2F-B107-73E72337A9A3}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
-    <tableColumn id="33" xr3:uid="{38676015-0F58-44D6-B371-9BA81ED28F5A}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
-    <tableColumn id="20" xr3:uid="{CF5DC892-6CDE-42D1-89D3-DEBAF257C463}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
+    <tableColumn id="1" xr3:uid="{CD8894E4-861B-451B-B3EC-9BEE97D48BE6}" name="CENTRO COSTO" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{03FFEBCC-4133-4785-B2ED-0F969C4997CC}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{D80ACFA5-D41C-41FB-92B0-11EDD4F64D6E}" name="RUBRO" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{EFC556A2-2D72-4253-9600-8CE35E984AE5}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{7049757E-772F-41C3-8BF3-C0C01C46D488}" name="META" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{5C8AAB29-4E02-4B70-949C-C65CE29C5EBD}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{C35851BE-DFF7-463D-B84D-42A581E7FAF1}" name="CLASIFICADOR" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{ECD464EE-685F-4C01-A737-8978535F592E}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
+    <tableColumn id="21" xr3:uid="{B789DFAB-F5EC-4443-9C3B-0B868F9F4B70}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
+    <tableColumn id="9" xr3:uid="{2CA21D75-7536-40B9-ADF7-5DD47BCE5480}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
+    <tableColumn id="22" xr3:uid="{BC7B12CF-8AE5-4B61-AE27-CF7B1514A53E}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
+    <tableColumn id="10" xr3:uid="{6A634EC6-F7D4-41EF-9AC5-041DA760323B}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
+    <tableColumn id="23" xr3:uid="{6E6AA6F7-7B15-4048-826D-C947B29BDCBA}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
+    <tableColumn id="11" xr3:uid="{22E41E12-9745-4FFF-A07C-4867B5D5009D}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
+    <tableColumn id="24" xr3:uid="{92EC0398-A408-415A-8F9F-E51F480A52ED}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
+    <tableColumn id="12" xr3:uid="{96D0A80C-5CAD-4559-A835-41CC6A6CB5C2}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
+    <tableColumn id="25" xr3:uid="{E5646102-F600-48FC-A3A3-FEA8B15FCAD0}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
+    <tableColumn id="13" xr3:uid="{C34B5692-6447-44F1-8784-D4F1D6A60346}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
+    <tableColumn id="26" xr3:uid="{3F89ECEA-4B0C-4902-904E-57F2C113D286}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
+    <tableColumn id="14" xr3:uid="{83F0AD0F-E438-4863-9C63-664AE3F9BD0F}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
+    <tableColumn id="27" xr3:uid="{05B771BB-1601-4136-B6A0-815A9A8CF56C}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
+    <tableColumn id="15" xr3:uid="{39F5A845-3999-4D57-9E65-C17B9F5BD770}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
+    <tableColumn id="28" xr3:uid="{8DA48587-E603-4631-8ABC-0DE952F494B9}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
+    <tableColumn id="16" xr3:uid="{4AB2F373-A050-4A41-B4B2-429C764F3A1B}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
+    <tableColumn id="29" xr3:uid="{E3579AE4-2BE8-4E4E-80B8-972B5B05D6A7}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
+    <tableColumn id="17" xr3:uid="{FBFD995E-C21D-482E-B391-2C7C7F288D42}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
+    <tableColumn id="30" xr3:uid="{AD51FF4B-3C3E-463C-8EC1-CD0C078B4683}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
+    <tableColumn id="18" xr3:uid="{67FD0547-8D68-4745-A704-FCB42EE8C5E8}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
+    <tableColumn id="32" xr3:uid="{78764F6D-4CF2-4C47-8476-6A326A7655F4}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
+    <tableColumn id="19" xr3:uid="{5AA5C26D-5106-4CBF-9E50-DEC84B11AB0E}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
+    <tableColumn id="33" xr3:uid="{EE81BFCE-12BC-4DCB-A99A-225F73295CBE}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
+    <tableColumn id="20" xr3:uid="{60A09DFB-1B4F-40B3-811C-35F55767D88F}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{DFC3F553-23E5-4E02-AD9C-E476F635BA4E}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
+    <tableColumn id="37" xr3:uid="{77D49134-39A8-4B7A-8701-19C9B8DCC7D2}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{759C49D8-89A2-4302-97E0-8D6822B51A69}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
+    <tableColumn id="43" xr3:uid="{B4E058E3-B47C-4722-9908-00A26872818A}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{EA1BF967-64A6-4E08-B22F-75D5A1D4FDEC}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
+    <tableColumn id="36" xr3:uid="{181F4016-7966-42A7-AD65-374FC24F336F}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{7542A2BE-AAE5-4DD2-A67D-6E7216C0A793}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
+    <tableColumn id="44" xr3:uid="{DDC9150C-B4C7-4DEA-8981-D438340F1646}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{EF535E8E-0530-47BB-A1C3-D350C565F83C}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
+    <tableColumn id="39" xr3:uid="{95210FB1-55F9-4CDE-959E-7FF622F6402E}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{4934ECE3-79C4-46DD-9108-6C3E7367AD26}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
+    <tableColumn id="45" xr3:uid="{85809F36-5D6A-4C30-BF43-E63CDF12842D}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{95B8D2B7-99B9-47AF-8E67-B75EAE73EFD2}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
+    <tableColumn id="38" xr3:uid="{727B7DE5-FA5A-4106-897A-69A03D9A603C}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{F5B75DAF-0F8D-40BA-8080-62332BEA8588}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
+    <tableColumn id="46" xr3:uid="{43E01B90-E45A-4145-8C30-707FFB2C68D7}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{B10D1BB6-325A-4C38-AA80-C527D8CF0F09}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
+    <tableColumn id="41" xr3:uid="{36D5C7A0-6358-49FA-8840-32454EEB89EE}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{F134A54D-674A-40D1-BE38-E06B3FD38088}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
+    <tableColumn id="31" xr3:uid="{4C208140-8AAD-4F71-9B9F-DD5B1B1BD24B}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{281EB04A-D7D4-426E-91C8-2C2EC9EAA03E}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
+    <tableColumn id="40" xr3:uid="{C7F0ABDD-8262-4F7C-AE59-B4C6F721E159}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{B69D19E5-3001-4E2A-8ED7-10901B6F422B}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
+    <tableColumn id="35" xr3:uid="{E13E59CF-2226-4BDB-B4AC-D25BFAEEBE8F}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{45BDA3C3-99AC-48D3-915E-C1E1003EB321}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
+    <tableColumn id="34" xr3:uid="{BE5318D9-11C2-4CDB-A302-ACB8965393FA}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9051,9 +9051,11 @@
       <c r="T46" s="33"/>
       <c r="U46" s="33"/>
       <c r="V46" s="33">
-        <v>1050</v>
-      </c>
-      <c r="W46" s="33"/>
+        <v>1030</v>
+      </c>
+      <c r="W46" s="33">
+        <v>1030</v>
+      </c>
       <c r="X46" s="33"/>
       <c r="Y46" s="33"/>
       <c r="Z46" s="33"/>
@@ -9064,7 +9066,7 @@
       <c r="AE46" s="33"/>
       <c r="AF46" s="33">
         <f>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="AG46" s="33">
         <f>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</f>
@@ -9084,11 +9086,11 @@
       </c>
       <c r="AK46" s="33">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</f>
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="AL46" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="AM46" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -9108,15 +9110,15 @@
       </c>
       <c r="AQ46" s="21">
         <f>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="AR46" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="AS46" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="AT46" s="116"/>
     </row>
@@ -10231,7 +10233,9 @@
       <c r="T57" s="31"/>
       <c r="U57" s="31"/>
       <c r="V57" s="31"/>
-      <c r="W57" s="31"/>
+      <c r="W57" s="31">
+        <v>1480</v>
+      </c>
       <c r="X57" s="31">
         <v>1480.02</v>
       </c>
@@ -10270,7 +10274,7 @@
       </c>
       <c r="AL57" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>1480</v>
       </c>
       <c r="AM57" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -10294,11 +10298,11 @@
       </c>
       <c r="AR57" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1480</v>
       </c>
       <c r="AS57" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>4360</v>
+        <v>5840</v>
       </c>
       <c r="AT57" s="116"/>
     </row>
@@ -13783,7 +13787,9 @@
       <c r="V88" s="33">
         <v>3000</v>
       </c>
-      <c r="W88" s="33"/>
+      <c r="W88" s="33">
+        <v>1914.8</v>
+      </c>
       <c r="X88" s="33"/>
       <c r="Y88" s="33"/>
       <c r="Z88" s="33"/>
@@ -13818,7 +13824,7 @@
       </c>
       <c r="AL88" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>1914.8</v>
       </c>
       <c r="AM88" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -13842,11 +13848,11 @@
       </c>
       <c r="AR88" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1914.8</v>
       </c>
       <c r="AS88" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>1914.8</v>
       </c>
       <c r="AT88" s="116"/>
     </row>
@@ -26927,7 +26933,9 @@
       <c r="V205" s="88">
         <v>8080</v>
       </c>
-      <c r="W205" s="88"/>
+      <c r="W205" s="88">
+        <v>8080</v>
+      </c>
       <c r="X205" s="88"/>
       <c r="Y205" s="88"/>
       <c r="Z205" s="88"/>
@@ -26962,7 +26970,7 @@
       </c>
       <c r="AL205" s="88">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>8080</v>
       </c>
       <c r="AM205" s="88">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -26986,11 +26994,11 @@
       </c>
       <c r="AR205" s="88">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>8080</v>
       </c>
       <c r="AS205" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>2020</v>
+        <v>10100</v>
       </c>
       <c r="AT205" s="116"/>
     </row>
@@ -29814,7 +29822,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C19:C22 C44 C153:C154 C91 C156 C11 C46:C52 C122 C126 C129:C130" xr:uid="{9700AED1-0919-4E15-ABFF-B9233D4F8A59}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C19:C22 C44 C153:C154 C91 C156 C11 C46:C52 C122 C126 C129:C130" xr:uid="{FFFB9FB4-E3DE-4FF4-8C4C-24309BD63F3C}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/presupuesto.xlsx
+++ b/data/presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC88E49-1806-4050-A3A1-715AE2EA4D93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5A6FB6-6F09-45BF-8C28-B0E148015A98}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3625,80 +3625,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C11C6284-A82A-41E3-A520-C36651C1A29D}" name="Programacion" displayName="Programacion" ref="A1:AS231" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
-  <autoFilter ref="A1:AS231" xr:uid="{8B1F43D4-8B91-4043-8A5E-AB42FC946F23}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0EA0D64-5083-4C7C-8008-224BCD03695C}" name="Programacion" displayName="Programacion" ref="A1:AS231" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45" headerRowCellStyle="Moneda" dataCellStyle="Moneda">
+  <autoFilter ref="A1:AS231" xr:uid="{B7ED704B-47D4-43F8-9CF7-C2448AE93B20}"/>
   <tableColumns count="45">
-    <tableColumn id="1" xr3:uid="{CD8894E4-861B-451B-B3EC-9BEE97D48BE6}" name="CENTRO COSTO" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{03FFEBCC-4133-4785-B2ED-0F969C4997CC}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{D80ACFA5-D41C-41FB-92B0-11EDD4F64D6E}" name="RUBRO" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{EFC556A2-2D72-4253-9600-8CE35E984AE5}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{7049757E-772F-41C3-8BF3-C0C01C46D488}" name="META" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{5C8AAB29-4E02-4B70-949C-C65CE29C5EBD}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{C35851BE-DFF7-463D-B84D-42A581E7FAF1}" name="CLASIFICADOR" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{ECD464EE-685F-4C01-A737-8978535F592E}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
-    <tableColumn id="21" xr3:uid="{B789DFAB-F5EC-4443-9C3B-0B868F9F4B70}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
-    <tableColumn id="9" xr3:uid="{2CA21D75-7536-40B9-ADF7-5DD47BCE5480}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
-    <tableColumn id="22" xr3:uid="{BC7B12CF-8AE5-4B61-AE27-CF7B1514A53E}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
-    <tableColumn id="10" xr3:uid="{6A634EC6-F7D4-41EF-9AC5-041DA760323B}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
-    <tableColumn id="23" xr3:uid="{6E6AA6F7-7B15-4048-826D-C947B29BDCBA}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
-    <tableColumn id="11" xr3:uid="{22E41E12-9745-4FFF-A07C-4867B5D5009D}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
-    <tableColumn id="24" xr3:uid="{92EC0398-A408-415A-8F9F-E51F480A52ED}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
-    <tableColumn id="12" xr3:uid="{96D0A80C-5CAD-4559-A835-41CC6A6CB5C2}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
-    <tableColumn id="25" xr3:uid="{E5646102-F600-48FC-A3A3-FEA8B15FCAD0}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
-    <tableColumn id="13" xr3:uid="{C34B5692-6447-44F1-8784-D4F1D6A60346}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
-    <tableColumn id="26" xr3:uid="{3F89ECEA-4B0C-4902-904E-57F2C113D286}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
-    <tableColumn id="14" xr3:uid="{83F0AD0F-E438-4863-9C63-664AE3F9BD0F}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
-    <tableColumn id="27" xr3:uid="{05B771BB-1601-4136-B6A0-815A9A8CF56C}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
-    <tableColumn id="15" xr3:uid="{39F5A845-3999-4D57-9E65-C17B9F5BD770}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
-    <tableColumn id="28" xr3:uid="{8DA48587-E603-4631-8ABC-0DE952F494B9}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
-    <tableColumn id="16" xr3:uid="{4AB2F373-A050-4A41-B4B2-429C764F3A1B}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
-    <tableColumn id="29" xr3:uid="{E3579AE4-2BE8-4E4E-80B8-972B5B05D6A7}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
-    <tableColumn id="17" xr3:uid="{FBFD995E-C21D-482E-B391-2C7C7F288D42}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
-    <tableColumn id="30" xr3:uid="{AD51FF4B-3C3E-463C-8EC1-CD0C078B4683}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
-    <tableColumn id="18" xr3:uid="{67FD0547-8D68-4745-A704-FCB42EE8C5E8}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
-    <tableColumn id="32" xr3:uid="{78764F6D-4CF2-4C47-8476-6A326A7655F4}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
-    <tableColumn id="19" xr3:uid="{5AA5C26D-5106-4CBF-9E50-DEC84B11AB0E}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
-    <tableColumn id="33" xr3:uid="{EE81BFCE-12BC-4DCB-A99A-225F73295CBE}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
-    <tableColumn id="20" xr3:uid="{60A09DFB-1B4F-40B3-811C-35F55767D88F}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
+    <tableColumn id="1" xr3:uid="{EA999080-DBE9-4830-A37B-F864171B3851}" name="CENTRO COSTO" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{1DF3DCAD-CB3E-4C92-B92F-BDFD5484986F}" name="NOMBRE DEL SERVICIO/BIEN A REQUERIR" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{AA871CA6-A6FC-459B-B909-F108889118D8}" name="RUBRO" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{EFE02A61-92A8-4709-AC5F-F8F8A10D60A4}" name="FUENTE DE FINANCIAMIENTO" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{0F11059D-08DC-499A-A05D-2D47432E0211}" name="META" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{C1EAC6F5-46B8-4348-875A-BFC5D7F69636}" name="GENÉRICA DE GASTO" dataDxfId="39" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{89B757B5-E7FD-48AF-BF4E-CE0BDE4AA425}" name="CLASIFICADOR" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{26803C28-B62A-4CC6-A96E-47408746926C}" name="ENERO" dataDxfId="37" dataCellStyle="Moneda"/>
+    <tableColumn id="21" xr3:uid="{CC1A70E3-6617-45F7-BC7B-9DB14185C344}" name="DEVENGADO ENERO" dataDxfId="36" dataCellStyle="Moneda"/>
+    <tableColumn id="9" xr3:uid="{57F8CE3C-004B-418F-AB0A-62E83A2DBFE9}" name="FEBRERO" dataDxfId="35" dataCellStyle="Moneda"/>
+    <tableColumn id="22" xr3:uid="{2BA49D69-8448-44B0-AC7E-A8DEE6C8A58E}" name="DEVENGADO FEBRERO" dataDxfId="34" dataCellStyle="Moneda"/>
+    <tableColumn id="10" xr3:uid="{6B469AD6-0BCC-489D-8A0D-46011BA7AF57}" name="MARZO" dataDxfId="33" dataCellStyle="Moneda"/>
+    <tableColumn id="23" xr3:uid="{51A941C7-1151-4758-B1B9-AA1D0E114320}" name="DEVENGADO MARZO" dataDxfId="32" dataCellStyle="Moneda"/>
+    <tableColumn id="11" xr3:uid="{F8D1ECEB-9400-4C5F-A97E-7C72D3545623}" name="ABRIL" dataDxfId="31" dataCellStyle="Moneda"/>
+    <tableColumn id="24" xr3:uid="{F2241149-2F58-487B-9060-2BDD3199A6DF}" name="DEVENGADO ABRIL" dataDxfId="30" dataCellStyle="Moneda"/>
+    <tableColumn id="12" xr3:uid="{01506CEB-B09B-4513-AF8E-5EBE5EFBD4E7}" name="MAYO" dataDxfId="29" dataCellStyle="Moneda"/>
+    <tableColumn id="25" xr3:uid="{6A4DB26F-F9E7-4F0D-BED1-568F716D9C5A}" name="DEVENGADO MAYO" dataDxfId="28" dataCellStyle="Moneda"/>
+    <tableColumn id="13" xr3:uid="{95DF12C6-C652-4182-BB01-50C470775839}" name="JUNIO" dataDxfId="27" dataCellStyle="Moneda"/>
+    <tableColumn id="26" xr3:uid="{DD05E1B8-6657-456A-9537-72A0F92B0D78}" name="DEVENGADO JUNIO" dataDxfId="26" dataCellStyle="Moneda"/>
+    <tableColumn id="14" xr3:uid="{D9E6E68C-8060-4348-B7BF-D112C83DD15C}" name="JULIO" dataDxfId="25" dataCellStyle="Moneda"/>
+    <tableColumn id="27" xr3:uid="{C01C0258-6121-426C-AC23-5C8BC0C079A8}" name="DEVENGADO JULIO" dataDxfId="24" dataCellStyle="Moneda"/>
+    <tableColumn id="15" xr3:uid="{0DF1C4A1-76FE-4ECB-90C7-7F301514D6D2}" name="AGOSTO" dataDxfId="23" dataCellStyle="Moneda"/>
+    <tableColumn id="28" xr3:uid="{25768D77-DBE7-4053-80E6-0ADFADC03B58}" name="DEVENGADO AGOSTO" dataDxfId="22" dataCellStyle="Moneda"/>
+    <tableColumn id="16" xr3:uid="{63BE8B52-6E9B-4918-BE80-AB4AAE52640D}" name="SEPTIEMBRE" dataDxfId="21" dataCellStyle="Moneda"/>
+    <tableColumn id="29" xr3:uid="{EF25696B-14CC-49DE-A271-C113AC6C8C00}" name="DEVENGADO SEPTIEMBRE" dataDxfId="20" dataCellStyle="Moneda"/>
+    <tableColumn id="17" xr3:uid="{2FE762BF-AD09-41F0-90C7-1BF4FF7C5AAC}" name="OCTUBRE" dataDxfId="19" dataCellStyle="Moneda"/>
+    <tableColumn id="30" xr3:uid="{072A7C71-B086-4828-AF10-E2B76D2C68CE}" name="DEVENGADO OCTUBRE" dataDxfId="18" dataCellStyle="Moneda"/>
+    <tableColumn id="18" xr3:uid="{F079A7B7-320E-4D0D-B61E-E138BE0BCE77}" name="NOVIEMBRE" dataDxfId="17" dataCellStyle="Moneda"/>
+    <tableColumn id="32" xr3:uid="{C3BB2550-37D2-49EF-8E3A-DB054F028657}" name="DEVENGADO NOVIEMBRE" dataDxfId="16" dataCellStyle="Moneda"/>
+    <tableColumn id="19" xr3:uid="{98F6581F-BF66-423A-AFA3-7981EAA19B8B}" name="DICIEMBRE" dataDxfId="15" dataCellStyle="Moneda"/>
+    <tableColumn id="33" xr3:uid="{2D4C283D-657F-459E-8898-4978EA1C046A}" name="DEVENGADO DICIEMBRE" dataDxfId="14" dataCellStyle="Moneda"/>
+    <tableColumn id="20" xr3:uid="{1F8DA4EA-FEDC-4AA8-91FB-3CC23384187C}" name="TOTAL PROGRAMADO" dataDxfId="13" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]+Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{77D49134-39A8-4B7A-8701-19C9B8DCC7D2}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
+    <tableColumn id="37" xr3:uid="{FD7FB367-0E00-4A95-8FC7-F7352DF75E60}" name="PRIMER TRIMESTRE" dataDxfId="12" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{B4E058E3-B47C-4722-9908-00A26872818A}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
+    <tableColumn id="43" xr3:uid="{3A977530-3F36-4DB5-810A-12802B273862}" name="DEVENGADO PRIMER TRIMESTRE" dataDxfId="11" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{181F4016-7966-42A7-AD65-374FC24F336F}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
+    <tableColumn id="36" xr3:uid="{A03436FA-DF6A-457A-BFFF-366EDB8275D3}" name="SEGUNDO TRIMESTRE" dataDxfId="10" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{DDC9150C-B4C7-4DEA-8981-D438340F1646}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
+    <tableColumn id="44" xr3:uid="{9240AD0F-EAF2-42B2-9E9C-A9ABBEAE54D8}" name="DEVENGADO SEGUNDO TRIMESTRE" dataDxfId="9" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{95210FB1-55F9-4CDE-959E-7FF622F6402E}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
+    <tableColumn id="39" xr3:uid="{3D2021B0-0842-4E6B-A1EA-3332E20BE144}" name="TERCER TRIMESTRE" dataDxfId="8" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{85809F36-5D6A-4C30-BF43-E63CDF12842D}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
+    <tableColumn id="45" xr3:uid="{A74AAB9B-1CBB-42E6-B8F5-67AACC405441}" name="DEVENGADO TERCER TRIMESTRE" dataDxfId="7" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{727B7DE5-FA5A-4106-897A-69A03D9A603C}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
+    <tableColumn id="38" xr3:uid="{99F1FFD5-A521-4A9D-93F2-3085FE0EBD3D}" name="CUARTO TRIMESTRE" dataDxfId="6" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{43E01B90-E45A-4145-8C30-707FFB2C68D7}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
+    <tableColumn id="46" xr3:uid="{7897F0AE-2065-4A76-B09F-5E4C58F4F310}" name="DEVENGADO CUARTO TRIMESTRE" dataDxfId="5" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{36D5C7A0-6358-49FA-8840-32454EEB89EE}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
+    <tableColumn id="41" xr3:uid="{6BE482EB-20DD-40A4-96D3-F2EA68FB94C7}" name="PRIMER SEMESTER" dataDxfId="4" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[ENERO]]+Programacion[[#This Row],[FEBRERO]]+Programacion[[#This Row],[MARZO]]+Programacion[[#This Row],[ABRIL]]+Programacion[[#This Row],[MAYO]]+Programacion[[#This Row],[JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{4C208140-8AAD-4F71-9B9F-DD5B1B1BD24B}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
+    <tableColumn id="31" xr3:uid="{6157A36C-F739-4A23-AC71-9BFD40EFC037}" name="DEVENGADO PRIMER SEMESTRE" dataDxfId="3" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{C7F0ABDD-8262-4F7C-AE59-B4C6F721E159}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
+    <tableColumn id="40" xr3:uid="{16577323-296B-48BA-AE26-170A2223E2D0}" name="SEGUNDO SEMESTRE" dataDxfId="2" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[JULIO]]+Programacion[[#This Row],[AGOSTO]]+Programacion[[#This Row],[SEPTIEMBRE]]+Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{E13E59CF-2226-4BDB-B4AC-D25BFAEEBE8F}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
+    <tableColumn id="35" xr3:uid="{131B565E-4EA6-486D-88CC-419093C2BFC1}" name="DEVENGADO SEGUNDO SEMESTRE" dataDxfId="1" dataCellStyle="Moneda">
       <calculatedColumnFormula>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{BE5318D9-11C2-4CDB-A302-ACB8965393FA}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
+    <tableColumn id="34" xr3:uid="{7D56A4C3-952C-4048-B30D-75DC3A4D95AE}" name="TOTAL DEVENGADO" dataDxfId="0" dataCellStyle="Moneda">
       <calculatedColumnFormula>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7962,7 +7962,7 @@
         <v>15600</v>
       </c>
       <c r="W36" s="17">
-        <v>7800</v>
+        <v>15600</v>
       </c>
       <c r="X36" s="17"/>
       <c r="Y36" s="17"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="AL36" s="19">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>7800</v>
+        <v>15600</v>
       </c>
       <c r="AM36" s="19">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -8022,11 +8022,11 @@
       </c>
       <c r="AR36" s="20">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>7800</v>
+        <v>15600</v>
       </c>
       <c r="AS36" s="21">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>22200</v>
+        <v>30000</v>
       </c>
       <c r="AT36" s="116"/>
     </row>
@@ -9479,7 +9479,9 @@
       <c r="V50" s="33">
         <v>13500</v>
       </c>
-      <c r="W50" s="33"/>
+      <c r="W50" s="33">
+        <v>13500</v>
+      </c>
       <c r="X50" s="33"/>
       <c r="Y50" s="33"/>
       <c r="Z50" s="33"/>
@@ -9514,7 +9516,7 @@
       </c>
       <c r="AL50" s="33">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]</f>
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="AM50" s="33">
         <f>Programacion[[#This Row],[OCTUBRE]]+Programacion[[#This Row],[NOVIEMBRE]]+Programacion[[#This Row],[DICIEMBRE]]</f>
@@ -9538,11 +9540,11 @@
       </c>
       <c r="AR50" s="21">
         <f>Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="AS50" s="33">
         <f>+Programacion[[#This Row],[DEVENGADO ENERO]]+Programacion[[#This Row],[DEVENGADO FEBRERO]]+Programacion[[#This Row],[DEVENGADO MARZO]]+Programacion[[#This Row],[DEVENGADO ABRIL]]+Programacion[[#This Row],[DEVENGADO MAYO]]+Programacion[[#This Row],[DEVENGADO JUNIO]]+Programacion[[#This Row],[DEVENGADO JULIO]]+Programacion[[#This Row],[DEVENGADO AGOSTO]]+Programacion[[#This Row],[DEVENGADO SEPTIEMBRE]]+Programacion[[#This Row],[DEVENGADO OCTUBRE]]+Programacion[[#This Row],[DEVENGADO NOVIEMBRE]]+Programacion[[#This Row],[DEVENGADO DICIEMBRE]]</f>
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="AT50" s="116"/>
     </row>
@@ -29822,7 +29824,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C19:C22 C44 C153:C154 C91 C156 C11 C46:C52 C122 C126 C129:C130" xr:uid="{FFFB9FB4-E3DE-4FF4-8C4C-24309BD63F3C}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C16:C17 C19:C22 C44 C153:C154 C91 C156 C11 C46:C52 C122 C126 C129:C130" xr:uid="{722CB669-D308-48C2-AB4C-E3A2475787D4}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
